--- a/data/trans_bre/IP04D$individual-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Estudios-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 11,36</t>
+          <t>-7,74; 11,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 9,99</t>
+          <t>-7,85; 9,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,45; -1,53</t>
+          <t>-23,84; 0,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,49; 102,74</t>
+          <t>-35,6; 111,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,56; 148,43</t>
+          <t>-51,91; 141,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-86,72; 2,32</t>
+          <t>-87,42; 11,86</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 0,91</t>
+          <t>-8,57; 0,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 5,9</t>
+          <t>-3,23; 6,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 1,06</t>
+          <t>-10,11; 0,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,45; 3,4</t>
+          <t>-27,26; 1,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 22,77</t>
+          <t>-10,58; 23,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,6; 8,81</t>
+          <t>-48,26; 4,99</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 4,14</t>
+          <t>-14,44; 3,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 16,83</t>
+          <t>0,05; 16,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 5,7</t>
+          <t>-11,12; 5,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 10,18</t>
+          <t>-29,64; 7,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 54,35</t>
+          <t>-0,09; 50,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,46; 22,41</t>
+          <t>-32,49; 23,11</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 0,57</t>
+          <t>-7,14; 0,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 6,94</t>
+          <t>-0,53; 7,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,45; -0,66</t>
+          <t>-9,43; -0,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 1,78</t>
+          <t>-21,34; 1,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 25,45</t>
+          <t>-1,79; 27,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,9; -3,77</t>
+          <t>-40,52; -3,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$individual-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Estudios-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 11,89</t>
+          <t>-7,9; 11,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 9,87</t>
+          <t>-7,85; 10,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 0,2</t>
+          <t>-24,47; -0,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 111,93</t>
+          <t>-37,07; 94,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,91; 141,1</t>
+          <t>-53,47; 153,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,42; 11,86</t>
+          <t>-88,37; -1,88</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 0,46</t>
+          <t>-8,67; 0,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 6,24</t>
+          <t>-3,25; 6,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 0,6</t>
+          <t>-10,79; 0,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 1,15</t>
+          <t>-27,41; 2,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 23,85</t>
+          <t>-10,78; 26,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 4,99</t>
+          <t>-49,55; 4,62</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 3,12</t>
+          <t>-13,68; 4,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 16,41</t>
+          <t>0,75; 16,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 5,8</t>
+          <t>-11,75; 6,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 7,55</t>
+          <t>-28,25; 9,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 50,96</t>
+          <t>1,72; 52,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,49; 23,11</t>
+          <t>-33,26; 23,5</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 0,38</t>
+          <t>-7,22; 0,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 7,31</t>
+          <t>-0,98; 6,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,43; -0,72</t>
+          <t>-9,24; 0,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 1,38</t>
+          <t>-21,47; 1,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 27,57</t>
+          <t>-3,48; 25,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,52; -3,64</t>
+          <t>-40,36; 0,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$individual-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Estudios-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción individual en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-12,34</t>
+          <t>-11,08</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-60,93%</t>
+          <t>-53,36%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 11,17</t>
+          <t>-7,66; 11,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 10,59</t>
+          <t>-8,22; 9,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,47; -0,97</t>
+          <t>-23,81; 1,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-37,07; 94,81</t>
+          <t>-35,49; 102,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,47; 153,6</t>
+          <t>-56,56; 148,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-88,37; -1,88</t>
+          <t>-83,61; 29,77</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-2,82</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-23,2%</t>
+          <t>-16,72%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 0,73</t>
+          <t>-8,37; 0,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 6,65</t>
+          <t>-3,91; 5,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 0,53</t>
+          <t>-9,03; 2,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 2,57</t>
+          <t>-26,45; 3,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 26,0</t>
+          <t>-12,46; 22,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,55; 4,62</t>
+          <t>-41,73; 17,99</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,74</t>
+          <t>-3,47</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,93%</t>
+          <t>-11,16%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 4,05</t>
+          <t>-13,97; 4,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 16,71</t>
+          <t>-0,23; 16,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 6,48</t>
+          <t>-11,84; 4,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 9,32</t>
+          <t>-28,25; 10,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 52,86</t>
+          <t>-0,53; 54,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 23,5</t>
+          <t>-33,38; 19,51</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-4,59</t>
+          <t>-3,65</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-22,31%</t>
+          <t>-17,73%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 0,44</t>
+          <t>-7,57; 0,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 6,79</t>
+          <t>-1,04; 6,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 0,06</t>
+          <t>-8,13; 0,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 1,48</t>
+          <t>-22,7; 1,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 25,5</t>
+          <t>-3,73; 25,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,36; 0,59</t>
+          <t>-35,11; 2,76</t>
         </is>
       </c>
     </row>
